--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487808_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487808_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7001</v>
+        <v>4.1555</v>
       </c>
       <c r="E2" t="n">
-        <v>4.724</v>
+        <v>3.9739</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0239</v>
+        <v>0.1816</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2106</v>
@@ -610,13 +610,13 @@
         <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4726</v>
+        <v>1.928</v>
       </c>
       <c r="T2" t="n">
-        <v>1.916</v>
+        <v>1.1659</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5565</v>
+        <v>0.7621</v>
       </c>
       <c r="V2" t="n">
         <v>1.3975</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>I. ROYO ARGOTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9654</v>
+        <v>2.61</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9271</v>
+        <v>0.2476</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9617</v>
+        <v>2.3624</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3894</v>
+        <v>0.8686</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7953</v>
+        <v>-3.0919</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1846</v>
+        <v>3.9605</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3655</v>
+        <v>1.2077</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0421</v>
+        <v>-2.2139</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3234</v>
+        <v>3.4216</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9762</v>
+        <v>-0.3391</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8374</v>
+        <v>-0.878</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1388</v>
+        <v>0.5389</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0812</v>
+        <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>3.703</v>
+        <v>0.5552</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4347</v>
+        <v>-0.1495</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2684</v>
+        <v>0.7047</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.1675</v>
+        <v>0.3538</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.3351</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8079</v>
+        <v>2.1136</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.722</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9788</v>
+        <v>1.3916</v>
       </c>
       <c r="G4" t="n">
         <v>1.1304</v>
@@ -766,13 +766,13 @@
         <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4725</v>
+        <v>0.7782</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0619</v>
+        <v>-0.0452</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4106</v>
+        <v>0.8234</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0437</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. DIENE</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5504</v>
+        <v>2.0748</v>
       </c>
       <c r="E5" t="n">
-        <v>0.765</v>
+        <v>3.2126</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7854</v>
+        <v>-1.1378</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5802</v>
+        <v>0.3894</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1768</v>
+        <v>-0.7953</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4033</v>
+        <v>1.1846</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4611</v>
+        <v>2.3655</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2236</v>
+        <v>1.0421</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7625</v>
+        <v>1.3234</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0412</v>
+        <v>-1.9762</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4005</v>
+        <v>-1.8374</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3592</v>
+        <v>-0.1388</v>
       </c>
       <c r="P5" t="n">
+        <v>1.0406</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-2.0812</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.0406</v>
+        <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9849</v>
+        <v>1.8124</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3851</v>
+        <v>0.7202</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5998</v>
+        <v>1.0922</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8137</v>
+        <v>-1.1675</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8137</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. ROYO ARGOTE</t>
+          <t>P. DIENE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4885</v>
+        <v>-0.0203</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6097</v>
+        <v>-0.3066</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0982</v>
+        <v>0.2863</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8686</v>
+        <v>-0.5802</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.0919</v>
+        <v>-0.1768</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9605</v>
+        <v>-0.4033</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2077</v>
+        <v>0.4611</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.2139</v>
+        <v>1.2236</v>
       </c>
       <c r="L6" t="n">
-        <v>3.4216</v>
+        <v>-0.7625</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3391</v>
+        <v>-1.0412</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.878</v>
+        <v>-1.4005</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5389</v>
+        <v>0.3592</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8325</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5663</v>
+        <v>2.4142</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0067</v>
+        <v>1.3135</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4404</v>
+        <v>1.1007</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3538</v>
+        <v>-0.8137</v>
       </c>
       <c r="W6" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1238</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6924</v>
+        <v>-0.4828</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.1019</v>
+        <v>-2.2446</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4094</v>
+        <v>1.7618</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5855</v>
@@ -1000,13 +1000,13 @@
         <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3399</v>
+        <v>0.8696</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6929</v>
+        <v>0.1643</v>
       </c>
       <c r="U7" t="n">
-        <v>0.353</v>
+        <v>0.7053</v>
       </c>
       <c r="V7" t="n">
         <v>0.6899</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.444</v>
+        <v>-3.1772</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.1347</v>
+        <v>-2.956</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3093</v>
+        <v>-0.2212</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5453</v>
@@ -1078,13 +1078,13 @@
         <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1494</v>
+        <v>1.1174</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6153</v>
+        <v>0.5634</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4659</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0437</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.947800000000001</v>
+        <v>-8.8454</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.6123</v>
+        <v>-5.8622</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.3355</v>
+        <v>-2.9832</v>
       </c>
       <c r="G9" t="n">
         <v>-4.7942</v>
@@ -1156,13 +1156,13 @@
         <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9643</v>
+        <v>0.1381</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0844</v>
+        <v>-0.3343</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1201</v>
+        <v>0.4724</v>
       </c>
       <c r="V9" t="n">
         <v>-3.1488</v>
@@ -1189,19 +1189,19 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.571900000000001</v>
+        <v>-1.571800000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2134</v>
+        <v>-3.213299999999998</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6414</v>
+        <v>1.6415</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.3274</v>
+        <v>-4.327400000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-7.878900000000001</v>
+        <v>-7.8789</v>
       </c>
       <c r="I10" t="n">
         <v>3.5514</v>
@@ -1213,7 +1213,7 @@
         <v>1.3288</v>
       </c>
       <c r="L10" t="n">
-        <v>2.1022</v>
+        <v>2.102200000000001</v>
       </c>
       <c r="M10" t="n">
         <v>-7.7585</v>
@@ -1225,7 +1225,7 @@
         <v>1.4492</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0811</v>
+        <v>-2.081099999999999</v>
       </c>
       <c r="Q10" t="n">
         <v>-13.5278</v>
@@ -1234,22 +1234,22 @@
         <v>11.4465</v>
       </c>
       <c r="S10" t="n">
-        <v>9.613099999999999</v>
+        <v>9.613100000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3984</v>
+        <v>3.3983</v>
       </c>
       <c r="U10" t="n">
         <v>6.214700000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.7762</v>
+        <v>-4.776199999999999</v>
       </c>
       <c r="W10" t="n">
         <v>3.4849</v>
       </c>
       <c r="X10" t="n">
-        <v>-8.261200000000001</v>
+        <v>-8.261199999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.5394</v>
+        <v>5.0037</v>
       </c>
       <c r="E11" t="n">
-        <v>2.917</v>
+        <v>2.8098</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6224</v>
+        <v>2.1939</v>
       </c>
       <c r="G11" t="n">
         <v>3.7664</v>
@@ -1312,13 +1312,13 @@
         <v>1.6649</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.792</v>
+        <v>-0.3277</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3824</v>
+        <v>-0.4895</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4096</v>
+        <v>0.1619</v>
       </c>
       <c r="V11" t="n">
         <v>1.9813</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. ORDOÑEZ OCHOA</t>
+          <t>J. HANNA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5015</v>
+        <v>2.8326</v>
       </c>
       <c r="E12" t="n">
-        <v>1.0522</v>
+        <v>1.9227</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4493</v>
+        <v>0.9099</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3274</v>
+        <v>1.3721</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2922</v>
+        <v>2.2922</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6197</v>
+        <v>-0.9201</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3073</v>
+        <v>1.9152</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2715</v>
+        <v>1.876</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5788</v>
+        <v>0.0392</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0201</v>
+        <v>-0.5431</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0207</v>
+        <v>0.4162</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0408</v>
+        <v>-0.9593</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4568</v>
+        <v>2.2893</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4974</v>
+        <v>2.2893</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.494</v>
+        <v>-1.1826</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.8062</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8383</v>
+        <v>-0.3764</v>
       </c>
       <c r="V12" t="n">
-        <v>2.2112</v>
+        <v>0.3538</v>
       </c>
       <c r="W12" t="n">
-        <v>2.4412</v>
+        <v>0.8137</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.23</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. HANNA</t>
+          <t>I. ORDOÑEZ OCHOA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1754</v>
+        <v>2.823</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8155</v>
+        <v>0.945</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3599</v>
+        <v>1.8779</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3721</v>
+        <v>0.3274</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2922</v>
+        <v>-0.2922</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9201</v>
+        <v>0.6197</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9152</v>
+        <v>0.3073</v>
       </c>
       <c r="K13" t="n">
-        <v>1.876</v>
+        <v>-0.2715</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0392</v>
+        <v>0.5788</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5431</v>
+        <v>0.0201</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4162</v>
+        <v>-0.0207</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9593</v>
+        <v>0.0408</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2893</v>
+        <v>1.4568</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2893</v>
+        <v>2.4974</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8398</v>
+        <v>-1.1725</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9134</v>
+        <v>-0.7629</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9264</v>
+        <v>-0.4096</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3538</v>
+        <v>2.2112</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8137</v>
+        <v>2.4412</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4599</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9558</v>
+        <v>1.1804</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2464</v>
+        <v>1.3536</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2906</v>
+        <v>-0.1731</v>
       </c>
       <c r="G14" t="n">
         <v>1.1728</v>
@@ -1546,13 +1546,13 @@
         <v>0.2081</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1951</v>
+        <v>0.0295</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0124</v>
+        <v>0.1195</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2075</v>
+        <v>-0.09</v>
       </c>
       <c r="V14" t="n">
         <v>-0.23</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. MARTIN MARTIN</t>
+          <t>S. TAIWO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1999</v>
+        <v>0.3765</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1958</v>
+        <v>1.362</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0041</v>
+        <v>-0.9856</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4148</v>
+        <v>1.4774</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7677</v>
+        <v>1.8146</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3528</v>
+        <v>-0.3372</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8518</v>
+        <v>3.1841</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7801</v>
+        <v>3.0273</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.9283</v>
+        <v>0.1568</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.437</v>
+        <v>-1.7067</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0124</v>
+        <v>-1.2127</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4245</v>
+        <v>-0.4939</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6244</v>
+        <v>0.6244</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7581</v>
+        <v>-1.1416</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7829</v>
+        <v>-0.7815</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0249</v>
+        <v>-0.3601</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1675</v>
+        <v>-0.5838</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. TAIWO</t>
+          <t>P. MARTIN MARTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2005</v>
+        <v>0.1373</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6835</v>
+        <v>0.1958</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8839</v>
+        <v>-0.0585</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4774</v>
+        <v>0.4148</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8146</v>
+        <v>1.7677</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3372</v>
+        <v>-1.3528</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1841</v>
+        <v>0.8518</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0273</v>
+        <v>1.7801</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1568</v>
+        <v>-0.9283</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7067</v>
+        <v>-0.437</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2127</v>
+        <v>-0.0124</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4939</v>
+        <v>-0.4245</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6244</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.7185</v>
+        <v>-0.8207</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.46</v>
+        <v>-0.7829</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2585</v>
+        <v>-0.0378</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5838</v>
+        <v>1.1675</v>
       </c>
       <c r="W16" t="n">
+        <v>1.1675</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0.5838</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0562</v>
+        <v>-0.6442</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9275</v>
+        <v>1.1419</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9837</v>
+        <v>-1.7861</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1438</v>
@@ -1780,13 +1780,13 @@
         <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4098</v>
+        <v>-0.9979</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3701</v>
+        <v>-1.1558</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0397</v>
+        <v>0.1579</v>
       </c>
       <c r="V17" t="n">
         <v>-1.1675</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.395</v>
+        <v>-1.2767</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.7709</v>
+        <v>-3.5566</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3759</v>
+        <v>2.2799</v>
       </c>
       <c r="G18" t="n">
         <v>-0.772</v>
@@ -1858,13 +1858,13 @@
         <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3536</v>
+        <v>-0.2352</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7705</v>
+        <v>-0.5562</v>
       </c>
       <c r="U18" t="n">
-        <v>0.417</v>
+        <v>0.3211</v>
       </c>
       <c r="V18" t="n">
         <v>-0.4776</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4063</v>
+        <v>-2.4968</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5053</v>
+        <v>-2.8268</v>
       </c>
       <c r="F19" t="n">
-        <v>0.099</v>
+        <v>0.33</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6697</v>
@@ -1936,13 +1936,13 @@
         <v>0.2081</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0959</v>
+        <v>0.0054</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1396</v>
+        <v>-0.1819</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0437</v>
+        <v>0.1873</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7423</v>
+        <v>-3.5065</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.2033</v>
+        <v>-4.989</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4609</v>
+        <v>1.4824</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6181</v>
@@ -2014,13 +2014,13 @@
         <v>1.6649</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1482</v>
+        <v>-0.9124</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0315</v>
+        <v>-0.8172</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1167</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>1.5213</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5717</v>
+        <v>4.4293</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6416</v>
+        <v>-1.641599999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>3.2133</v>
+        <v>6.0707</v>
       </c>
       <c r="G21" t="n">
         <v>4.3273</v>
@@ -2092,19 +2092,19 @@
         <v>13.5274</v>
       </c>
       <c r="S21" t="n">
-        <v>-9.613199999999999</v>
+        <v>-6.7557</v>
       </c>
       <c r="T21" t="n">
-        <v>-6.214500000000001</v>
+        <v>-6.214599999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-3.3985</v>
+        <v>-0.5408999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>4.7762</v>
       </c>
       <c r="W21" t="n">
-        <v>8.261099999999999</v>
+        <v>8.261100000000001</v>
       </c>
       <c r="X21" t="n">
         <v>-3.485</v>
